--- a/z_RequestData/jobsearch_data104.xlsx
+++ b/z_RequestData/jobsearch_data104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6446,10 +6446,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A112" t="n">
+        <v>20260806</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6504,10 +6502,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>20260727</t>
-        </is>
+      <c r="A113" t="n">
+        <v>20260727</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6561,10 +6557,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A114" t="n">
+        <v>20260807</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -6614,10 +6608,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A115" t="n">
+        <v>20260805</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -6670,10 +6662,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>20260720</t>
-        </is>
+      <c r="A116" t="n">
+        <v>20260720</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -6722,10 +6712,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>20260727</t>
-        </is>
+      <c r="A117" t="n">
+        <v>20260727</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -6777,10 +6765,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A118" t="n">
+        <v>20260804</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -6832,10 +6818,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A119" t="n">
+        <v>20260803</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -6889,10 +6873,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A120" t="n">
+        <v>20260804</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -6944,10 +6926,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A121" t="n">
+        <v>20260805</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -6998,10 +6978,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A122" t="n">
+        <v>20260803</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -7051,10 +7029,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A123" t="n">
+        <v>20260806</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -7105,10 +7081,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A124" t="n">
+        <v>20260807</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -7159,10 +7133,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>20260701</t>
-        </is>
+      <c r="A125" t="n">
+        <v>20260701</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -7214,10 +7186,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A126" t="n">
+        <v>20260805</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -7268,10 +7238,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>20260529</t>
-        </is>
+      <c r="A127" t="n">
+        <v>20260529</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -7323,10 +7291,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A128" t="n">
+        <v>20260806</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -7376,10 +7342,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A129" t="n">
+        <v>20260803</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -7430,10 +7394,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A130" t="n">
+        <v>20260807</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7484,10 +7446,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A131" t="n">
+        <v>20260805</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -7557,10 +7517,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A132" t="n">
+        <v>20260810</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -7614,10 +7572,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A133" t="n">
+        <v>20260806</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -7688,10 +7644,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A134" t="n">
+        <v>20260810</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -7744,10 +7698,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A135" t="n">
+        <v>20260810</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -7803,10 +7755,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A136" t="n">
+        <v>20260807</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -7858,10 +7808,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>20260728</t>
-        </is>
+      <c r="A137" t="n">
+        <v>20260728</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -7912,10 +7860,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>20260731</t>
-        </is>
+      <c r="A138" t="n">
+        <v>20260731</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -7968,10 +7914,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A139" t="n">
+        <v>20260805</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -8026,10 +7970,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>20260508</t>
-        </is>
+      <c r="A140" t="n">
+        <v>20260508</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -8083,10 +8025,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A141" t="n">
+        <v>20260804</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -8138,10 +8078,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A142" t="n">
+        <v>20260803</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -8192,10 +8130,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>20260730</t>
-        </is>
+      <c r="A143" t="n">
+        <v>20260730</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -8249,10 +8185,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A144" t="n">
+        <v>20260803</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -8303,10 +8237,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A145" t="n">
+        <v>20260810</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -8356,10 +8288,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A146" t="n">
+        <v>20260803</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -8409,10 +8339,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A147" t="n">
+        <v>20260807</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -8464,10 +8392,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A148" t="n">
+        <v>20260805</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -8519,10 +8445,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>20260731</t>
-        </is>
+      <c r="A149" t="n">
+        <v>20260731</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -8573,10 +8497,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A150" t="n">
+        <v>20260803</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -8627,10 +8549,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A151" t="n">
+        <v>20260805</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -8682,10 +8602,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A152" t="n">
+        <v>20260806</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -8737,10 +8655,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A153" t="n">
+        <v>20260804</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -8792,10 +8708,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A154" t="n">
+        <v>20260807</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -8850,10 +8764,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>20260729</t>
-        </is>
+      <c r="A155" t="n">
+        <v>20260729</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -8906,10 +8818,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A156" t="n">
+        <v>20260805</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -8962,10 +8872,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A157" t="n">
+        <v>20260810</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -9016,10 +8924,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>20260707</t>
-        </is>
+      <c r="A158" t="n">
+        <v>20260707</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -9071,10 +8977,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A159" t="n">
+        <v>20260805</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -9123,10 +9027,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A160" t="n">
+        <v>20260803</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -9208,10 +9110,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A161" t="n">
+        <v>20260810</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -9264,10 +9164,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A162" t="n">
+        <v>20260804</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -9319,10 +9217,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A163" t="n">
+        <v>20260810</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -9373,10 +9269,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A164" t="n">
+        <v>20260806</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -9427,10 +9321,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A165" t="n">
+        <v>20260804</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -9482,10 +9374,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A166" t="n">
+        <v>20260805</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -9537,10 +9427,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>20260727</t>
-        </is>
+      <c r="A167" t="n">
+        <v>20260727</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -9591,10 +9479,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A168" t="n">
+        <v>20260803</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -9645,10 +9531,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A169" t="n">
+        <v>20260804</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -9701,10 +9585,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A170" t="n">
+        <v>20260807</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -9756,10 +9638,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A171" t="n">
+        <v>20260803</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -9812,10 +9692,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A172" t="n">
+        <v>20260807</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -9869,10 +9747,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>20260728</t>
-        </is>
+      <c r="A173" t="n">
+        <v>20260728</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -9925,10 +9801,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A174" t="n">
+        <v>20260806</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -9978,10 +9852,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A175" t="n">
+        <v>20260804</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -10031,10 +9903,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A176" t="n">
+        <v>20260806</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -10085,10 +9955,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A177" t="n">
+        <v>20260804</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -10141,10 +10009,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>20260808</t>
-        </is>
+      <c r="A178" t="n">
+        <v>20260808</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -10201,10 +10067,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A179" t="n">
+        <v>20260804</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -10254,10 +10118,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>20260729</t>
-        </is>
+      <c r="A180" t="n">
+        <v>20260729</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -10307,10 +10169,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A181" t="n">
+        <v>20260810</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -10363,10 +10223,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>20260727</t>
-        </is>
+      <c r="A182" t="n">
+        <v>20260727</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -10418,10 +10276,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A183" t="n">
+        <v>20260806</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -10471,10 +10327,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A184" t="n">
+        <v>20260807</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -10526,10 +10380,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>20260808</t>
-        </is>
+      <c r="A185" t="n">
+        <v>20260808</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -10585,10 +10437,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A186" t="n">
+        <v>20260810</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -10640,10 +10490,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A187" t="n">
+        <v>20260810</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -10693,10 +10541,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A188" t="n">
+        <v>20260804</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -10748,10 +10594,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A189" t="n">
+        <v>20260806</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -10803,10 +10647,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A190" t="n">
+        <v>20260807</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -10862,10 +10704,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>20260808</t>
-        </is>
+      <c r="A191" t="n">
+        <v>20260808</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -10916,10 +10756,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A192" t="n">
+        <v>20260806</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -10970,10 +10808,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A193" t="n">
+        <v>20260804</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -11031,10 +10867,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>20260807</t>
-        </is>
+      <c r="A194" t="n">
+        <v>20260807</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -11087,10 +10921,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A195" t="n">
+        <v>20260810</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -11140,10 +10972,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A196" t="n">
+        <v>20260804</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -11198,10 +11028,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A197" t="n">
+        <v>20260804</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -11252,10 +11080,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>20260806</t>
-        </is>
+      <c r="A198" t="n">
+        <v>20260806</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -11307,10 +11133,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A199" t="n">
+        <v>20260804</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -11362,10 +11186,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A200" t="n">
+        <v>20260810</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -11418,10 +11240,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A201" t="n">
+        <v>20260803</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -11471,10 +11291,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>20260731</t>
-        </is>
+      <c r="A202" t="n">
+        <v>20260731</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -11527,10 +11345,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A203" t="n">
+        <v>20260810</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -11582,10 +11398,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>20260721</t>
-        </is>
+      <c r="A204" t="n">
+        <v>20260721</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -11639,10 +11453,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>20260805</t>
-        </is>
+      <c r="A205" t="n">
+        <v>20260805</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -11694,10 +11506,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A206" t="n">
+        <v>20260804</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -11749,10 +11559,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>20260727</t>
-        </is>
+      <c r="A207" t="n">
+        <v>20260727</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -11805,10 +11613,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A208" t="n">
+        <v>20260804</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -11862,10 +11668,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>20260810</t>
-        </is>
+      <c r="A209" t="n">
+        <v>20260810</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -11915,10 +11719,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A210" t="n">
+        <v>20260804</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -11969,10 +11771,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A211" t="n">
+        <v>20260804</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -12026,10 +11826,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A212" t="n">
+        <v>20260803</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -12081,10 +11879,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A213" t="n">
+        <v>20260804</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -12140,10 +11936,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A214" t="n">
+        <v>20260804</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -12196,10 +11990,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>20260809</t>
-        </is>
+      <c r="A215" t="n">
+        <v>20260809</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -12250,10 +12042,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>20260728</t>
-        </is>
+      <c r="A216" t="n">
+        <v>20260728</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -12305,10 +12095,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>20260428</t>
-        </is>
+      <c r="A217" t="n">
+        <v>20260428</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -12359,10 +12147,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A218" t="n">
+        <v>20260804</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -12415,10 +12201,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>20260803</t>
-        </is>
+      <c r="A219" t="n">
+        <v>20260803</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -12469,10 +12253,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>20260804</t>
-        </is>
+      <c r="A220" t="n">
+        <v>20260804</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -12523,10 +12305,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>20260730</t>
-        </is>
+      <c r="A221" t="n">
+        <v>20260730</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -12573,6 +12353,6193 @@
       <c r="J221" t="inlineStr">
         <is>
           <t>https://www.104.com.tw/job/8ppdw</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>&lt; 電子工程師 &gt; EE Engineer 物聯網無線模組產業</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>勁達國際電子股份有限公司</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>新北市中和區 中正路788-1號8樓</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>4年以上</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Raytac 是台灣領先的無線模組製造商，技術涵蓋 藍牙、Wi-Fi 與 LoRa，據點橫跨台灣與美國加州，深耕全球市場。
+我們正在尋找熱愛無線技術的電子工程師(EE Engineer)，加入我們的開發團隊，共同打造全球領先的無線模組產品。</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8iupv</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>AI軟體設計工程師（日本東京）</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>株式会社ビジネスフューチャーズ</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>日本 (依照公司規定分派，公司社內或者公司的客戶社內)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 150,000元</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>1. 從事AI人工智能產品研發（具有大模型，多模態的工作經驗或者知識等）
+具有各種演算法以及本地端知識庫，向量化資料庫的設計，優化，改進和模型的訓練經驗或知識等（RAG等）
+2. 從事網絡程式設計和研發
+3. 精通Java，Python，</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8r3tf</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>研發類-Drone Data Engineer 無人機資料工程師</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>中光電智能機器人股份有限公司</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>新竹市 力行路11號</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pipeline &amp; Automation)
+      a) 評估並建立適合資料庫架構與資料管理系統。
+      b) 設計並實作端到端自動化數據擷取與傳輸流程。
+2. 異質底層日誌解析與標準化 (Log Reverse Engineering</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96ph5</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>晁昇量化資本股份有限公司</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 四維三路225號1樓</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>月薪 36,000 ~ 50,000元</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>為了持續推動技術創新與策略優化，我們正在尋找金融資料研究員，協助團隊透過金融資料分析、AI 輔助研究與程式化工具，開發並尋找交易機會。
+【工作內容】
+研究並整理各類金融商品的交易規則與市場資料。
+使用 AI Coding (主要開發語言為</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/927l9</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>【國泰投信】資料工程師 Data Engineer_I00022210</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Kubernetes）。
+5. 實現湖倉一體（Lakehouse）與存算分離架構。
+【必要條件】
+1. 1 年以上資料工程或資料分析經驗，具備資料處理或資料分析的程式開發能力。
+2. 具備 Python 軟體開發或資料處理經驗。
+3. 具備 Linux 系</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbni</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Position Impact：
+資料工程師的核心價值在於設計、建置並維護整體的數據解決方案，確保全公司的數據具備高可用性、可靠性及可擴充性。在此職位中，您將處理大規模數據庫，主動識別潛在風險，並開發能提升數據效能與品質的解決方案。您將與後端工程師</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ti6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>【Data Engineer】 資料工程師</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>新加坡商昇新科技股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>台北市內湖區 瑞湖街58號5樓</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>我們正處於數據架構升級的關鍵階段。尋找一位數據工程專家與我們共同重新定義數據流。
+你將負責冷熱數據分離架構的落地，並優化我們的 Data Warehouse 架構，確保在海量數據環境下，數據依然能兼具查詢效能與成本。
+【你將面臨的核心技術挑戰】</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x352</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>德義資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市萬華區 </t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>【職務需求】
+1. 以 Data Engineering 為主，包含 hands-on data pipeline、ETL、data modeling、以及上游系統整合經驗。
+2. 需具備資料整合、資料品質與資料模型設計能力。
+3. 熟悉</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91q0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>文境資科股份有限公司</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Data Engineer/ 資料工程師
+1.資料稽核(Data Auditing)、收集(Data Collection)、整合作業(Data Integration) 等資料分析前處理作業
+2.有MS SQL server、SSIS、SSRS</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7g1tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ETL 資料工程師/大數據工程師</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>歐立威科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>台北市大同區 鄭州路87號11樓之1</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 100,000元</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Pentaho PDI、Talend、Informatica、Microsoft SSIS 等）進行數據抽取、轉換與載入，確保資料正確性與完整性。
+3.熟悉 Python 或 Java 等程式語言，能撰寫 ETL 腳本與自動化流程。
+4.設計並維護 Data</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ugrj</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>資料工程師(Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>貝伯盈智慧運營有限公司</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>台中市南區 福順里平順街200號1樓</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>工作內容
+•設計與開發針對各類網路媒體與社群平台的資料蒐集系統
+•維護與優化現有爬蟲，應對頁面改版、防護機制調整等變動
+•建立排程任務，監控資料蒐集品質與異常狀況
+•將蒐集資料寫入大數據資料庫，配合後端需求設計儲存結構
+•分析蒐集失敗根因，針對不</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92ier</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>澧曜數據有限公司</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號2樓</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發/維護/設計處理數據架構與服務以及部署服務。
+2. 負責ETL（數據提取、轉換、加載）流程設計，包括數據清洗、預處理及自訂程式開發。
+3. 擁有CI/CD經驗，熟悉Jenkins、GitLab、Airflow等CI/CD工具和流程。
+</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8dclx</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>【台北】數據工程師Data Engineer — "Data Infrastructure Architect"</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>創智動能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>台北市中正區 八德路1段23號9樓</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>至數據倉儲或資料湖。 
+   確保數據準確性與一致性，並優化數據處理效能。
+Data Transformation and Integration
+Design and implement data transformation processes</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8kgsh</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>資深資料工程師</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>聯樂數位行銷股份有限公司</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>廣告行銷公關業</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段285號4樓</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>【職務內容】
+1. 負責資料的雲端基礎架構設計與演進，涵蓋資料流、整合處理、監控狀態等。
+2. 開發和串接API，提供穩定、可重複使用的資料服務。。
+3. 兼顧業務成長與工程實作需求，將資料相關能力平台化，提供穩定、可重複使用的基礎服務。
+4.</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92g11</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>【國泰投信】資深資料工程師 Senior Data Engineer_I00022193</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>國泰證券投資信託股份有限公司</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>證券及期貨業</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號6樓</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>定 ETL 資料處理流程（資料存取、蒐集、處理和儲存）的開發標準與最佳實踐，確保系統的高效、穩定與可擴展性。
+4. 負責數據架構的效能優化，指導並帶領團隊解決技術難題。
+【必要條件】
+1. 5 年以上資料工程經驗，具備分散式系統與容器化經驗。
+2</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8qbnl</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>重高科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>台北市大安區 忠孝東路四段162號12樓之2</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 60,000元</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Technical Skills)--
+我們希望候選人在以下多數領域具備實作經驗：
+1. Python：精通 Python，特別是在資料工程與自動化流程的應用（而不僅僅是撰寫簡單腳本或 ML 模型）。
+2. SQL：專家級別，具備 BigQuery 或類似雲端資料</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8yvez</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>資料工程師/BI工程師</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>揚明光學股份有限公司_YoungOptics Inc.</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>光學器材製造業</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>新竹市 科學園區新安路7號</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>1. 儀表板 / BI 報表開發：
+￭ 使用 FineReport / MS SQL SSRS / Power BI 來製作儀表板與 KPI 報表
+￭ 與業務單位合作，建立資料模型並提供有洞察力的視覺化分析
+2. SAP BW / 資料倉儲管理：</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8q2xn</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>永慶房產集團_永慶房屋仲介股份有限公司</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>不動產經營業</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段77號12樓</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>永慶房產集團為房仲產業龍頭，用科技創新引領創新變革，歡迎IT領域的優秀夥伴加入!
+工作內容如下：
+1.規劃集團資料流程，達成資料整合綜效。
+2.建置企業數據中台，管控集團資料倉儲品質與正確性。
+3.與資料分析師協同合作，進行資料分析前處理，提供</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/78pf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>【AI Lab】資深數據工程師 Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>愛卡拉互動媒體股份有限公司</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市中山區 </t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>【Responsibilities】
+- Design, build, and maintain scalable data pipelines that meet evolving product and analytics needs.
+- Identify, design, and implement internal process improvements: automating manual processes, optimizing data delivery, re-designing infrastructure for greater scalability, etc.
+- Create data tools that enable analytics and data scientist team members to build and ship faster.
+- Build and maintain the services that deliver our data to product, analytics, and external consumers.
+- Partner with data and analytics teams to evolve our data infrastructure.
+- Support cross functional, cross BU data integration tasks.
+【Must to Have】
+- Bachelor's degree in Computer Science, Engineering, or a related field, or equivalent practical experience; Master's is a plus
+- Strong proficiency in Python 3.10+ and shell scripting (Bash), with 5+ years of backend / data engineering experience and 3+ years owning production data pipelines
+- Experience with workflow orchestration tools, e.g. Argo Workflow, Airflow, Dagster
+- Experience with RDBMS, OLAP, and search databases, e.g. PostgreSQL, StarRocks (or BigQuery / ClickHouse / Snowflake / Druid), Elasticsearch
+- Experience with backend API development and deployment, e.g. gRPC, REST (FastAPI)
+- Experience deploying and operating services on Kubernetes with Docker
+- Comfortable developing, deploying, and debugging in Linux environments
+【Nice to Have】
+- Basic knowledge of machine learning algorithms
+- Basic knowledge of Data Lake and Data Warehouse Design
+- Experience with streaming processing systems, e.g. Kafka, Apache Flink, Cloud Dataflow, Apache Beam, Pub/Sub
+- Experience with Go programming language
+- Experience with gRPC and Protocol Buffers
+- Experience with production-grade operations — monitoring, debugging, and maintaining your own work after deployment</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91m1t</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>行銷部-數據工程師 ( Data Engineer )</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>動力，能適應快速變化的技術環境，持續精進技能 
+4. 勇於挑戰創新 - 保持開放心態，不設限自己的發展，樂於嘗試新技術與跨領域合作
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、資料庫、CSV、</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7xcgt</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>三竹資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>台北市中山區 新生北路二段39號11F</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 排程管理經驗、DB 帳號權限控管經驗，或有處理高併發金融資料流之經驗。
+職務內容：
+1. 本職務屬於產品任務，配合研發團隊發展金融科技應用之日常資料工程，並負責穩定性維護與效能優化。
+2. 參與設計高可靠性（High Availability）</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mtc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer【數位數據發展本部】</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>東南旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路二段60號</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>統性整合資料支撐分析與AI應用的發展
+●	建置優化Data Pipeline，並建立資料品質監控管理機制，確保資料品質和效率
+●	與DA / DS 協作，開發實作數據 / AI產品，參與模型的部署上線與維運
+●	協作工程師設計大規模資料遷移，參與</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tbys</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>【桃園A10、大興新建社宅】職安高級工程師</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>皆豪實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>土木工程業</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>桃園市蘆竹區 【工程所在地】</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>月薪 55,000元以上</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.現場施工管理及協調。
+2.執行安全衛生督導及稽核。
+3.工地勞工安全衛生管理及文書業務。
+4.職安衛資料統計整理及呈報。
+5.召開工地安衛環保相關會議。
+6.其他經主管指派交辦事項。
+</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8avwr</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>半導體 IC 資深測試工程師(擴大徵才)</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>全智科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>其他半導體相關業</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>新竹市 新竹科學園區科技五路六號7樓</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>月薪 38,500元以上</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>試工程師工作內容：
+1.客戶需求:
+- 與客戶溝通ATE機台測試驗證細節 
+- 產品配件驗證
+- 工程生產異常分析
+- 工程測試結果確認及回報
+- 配合客戶需求進行異常修正並主動解決問題 
+2.NPI導入需求:
+- 測試生產線無塵室(1K and</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7p7t6</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ETL資料工程師</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>緯德科技股份有限公司 (TechLink Corporation)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>台北市松山區 敦化北路207號8F-13</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>- 熟悉資料庫之SQL語法執行ETL資料轉換作業(ETL Job Developing、IBM DataStage、Informatica PowerCenter、Microsoft SSIS、Trinity)實務經驗1年以上。
+- 熟悉資料庫安</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/5e9ei</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>資訊部-資深數據工程師Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>王品餐飲股份有限公司</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>餐館業</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>台中市西區 民龍里台灣大道2段218號29樓</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>王品集團 誠徵【資訊部-資深數據工程師】
+【職務說明】
+我們正在尋找具備資料工程與資料庫實務能力的資深數據工程師，負責企業多來源資料的收集、清理、轉換與整合，並設計、建置及優化穩定且可維護的資料管線與資料倉儲。
+此職務以 Data</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92mxb</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>數據工程師｜打造零售界的神級Data Build</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>你是資料界的打怪高手嗎？
+我們正在尋找一位能將數據煉金的工程師，一起升級零售產業的數據系統，從地端到雲端，穩定輸出、精準命中！
+這份工作不只是 coding，更是策略規劃、技術架構與商業價值的 combo 技。
+如果你喜歡優化效能、挑戰架構、解任</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4bma8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師 (桃園龜山近林口長庚)</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>桃園市龜山區 頂湖路33號 (近林口長庚)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>職務影響力
+本職位以資料工程與分析平台建設為核心，負責打造穩定、可擴展且可維運的工程數據基礎設施，作為工程與研發團隊進行數據決策的關鍵支撐。透過提升資料管道品質、系統自動化與整體擴展性，使資料分析工程師與工程團隊能在一致且可信的數據基礎上，規模化</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wzpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>數據工程師(Data Engineer) - Python/API開發/ETL</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>果友科技有限公司</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備後端思維的數據工程師，打造數據產品與並與分析客戶團隊合作，建置高品質的數據供應與自動化環境。
+你的主要任務是確保數據能穩定流動、被正確處理與自動化運作，成為支撐企業決策與AI應用的堅實基礎。
+【工作內容】
+1. 設計、開發與</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8thk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據架構工程師) – (數數發中心, DDT)</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>台北市大安區 敦化南路二段39號</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>【關於我們】
+我們是國泰產險的資料科學（DS）團隊，使命在於持續進化數據應用，創造並釋放數據價值。目前正在藉由數據上雲、數據治理與 AI 技術應用，推動由底層架構到業務應用的全端數據生態建構與 AI 轉型準備。
+我們尋找認同以下團隊文化的夥伴：</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8opms</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>雲端數據工程師</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>君綺生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>美容／美體業</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>台北市信義區 松智路1號</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>部門介紹:
+我們是集團組織擴編成立的新部門, 在這工作你將會體驗全雲的工作環境, 包含AWS雲端服務及工具, 在工作中學習專案管理、資料庫管理、雲端服務等技術
+工作內容
+1. 參與雲端數據架構發展規劃，設計資料處理、儲存、分析架構，以符合數據</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mcsu</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>愛德萬互聯科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>桃園市蘆竹區 內溪路47號</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">◎主要工作內容包括：
+Data Analytics &amp; Business Insights
+•	Analyze large and complex datasets from business and manufacturing systems to identify trends, patterns, exceptions, and improvement opportunities.
+•	Translate business challenges into data requirements, analytical approaches, and actionable recommendations.
+Data Solution Planning &amp; Project Delivery
+•	Conduct requirement analysis and assess data sources, dependencies, risks, and solution feasibility for assigned data initiatives.
+•	Define solution scope, data models, integration approaches, deliverables, and validation criteria for data projects.
+Data Architecture &amp; Engineering Collaboration
+•	Design scalable data models, Data Warehouse structures, Data Marts, and reusable datasets across enterprise and operational systems.
+Enterprise Applications &amp; Systems Integration
+•	Design cross-system data mappings, interface requirements, reconciliation controls, and exception-handling mechanisms.
+•	Support the development and maintenance of internal data applications, system interfaces, and lightweight services using C#/.NET technologies such as WinForms and ASP.NET Web Forms.
+•	Support Oracle ERP-related data integration and application services, including Oracle Database connectivity, SQL and PL/SQL development, data interfaces, and integration with internal systems.
+Visualization &amp; Reporting
+•	Develop interactive dashboards, management reports, and operational visualizations using Power BI and other analytics tools.
+◎需求條件：
+•	Bachelor's degree in Information Technology, Information Management, Software Engineering, or a related information systems field.
+•	Minimum 3 years of experience in data analytics, business intelligence, data engineering, database development, enterprise applications, or related disciplines.
+•	Hands-on experience with Oracle Database and PL/SQL, including database objects and stored procedures, as well as Microsoft SQL Server database development, performance tuning, and maintenance.
+•	Hands-on experience in data modeling and Data Warehouse or Data Mart design, with practical exposure to cross-system data integration.
+•	Experience developing dashboards, management reports, or analytical applications using Power BI, Tableau, or similar platforms.
+•	C# / ASP.NET Application Development
+</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94jv3</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TAC｜AI 資料工程師（RAG／資料品質）</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>新夥伴科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>台中市西區 忠明南路497號13樓</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>年薪 600,000 ~ 1,000,000元</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>【職務說明】
+我們正在尋找一位細心、擅長整理資訊，並能理解基本技術內容的夥伴。
+你將協助整理客服紀錄、FAQ、KB 及技術文件，將零散資訊轉換成清楚、標準化且可供 AI 使用的知識資料。
+【工作內容】
+1. 學習並了解公司產品、功能及常見</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/95lk2</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>統一超數據工程師 (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>統一超商股份有限公司</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>百貨相關業</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>台北市信義區 東興路65號2樓</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>月薪 37,770 ~ 52,000元</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>•雲端數據架構實踐與遷移： 執行地端資料庫遷移至 GCP 雲端平台（如 BigQuery, GCS,Cloud Run 等）之開發與架構設計，確保系統穩定、權限控管及資源成本優化。
+•巨量資料 ETL/ELT 流程開發： 設計、開發並維護自動化</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92uqv</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>AI/資料工程師</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>芮比智能科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>自動控制相關業</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>雲林縣斗南鎮 林子路1-1號</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+3.建置與維運 RAG／向量資料庫應用,串接本地與雲端模型,設計知識檢索、prompt 與 Agent 流程。
+4.資料工程:設計資料蒐集、清理、轉換(ETL)與儲存流程,處理 CSV／Excel／JSON／資料庫匯出檔及設備即時資料。
+5.協助智</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/95967</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>AIR SPACE_新地國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品批發業</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>台北市士林區 中山北路五段(近士林捷運站210公尺)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>AIR SPACE為台灣第一女裝品牌，
+我們提供安心的工作環境、人才培育訓練課程，
+願您能成為永續經營的共同夥伴，歡迎加入AIR SPACE團隊！
+【我們在找什麼樣的你】
+熟悉資料庫、ETL 流程與數據建模，能有效整理、清理與分析大量數據，</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8fvcr</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>【南部高薪獵才_高發揮空間資料工程師】可討論半遠端工作、0&gt;1建置機會、數位轉型、扁平化組織可直接與負責人溝通_TCP_860</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>藝珂人事顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>人力仲介代徵</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>高雄市前鎮區 忠孝東路5段68號10樓B區</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>管理及資訊化管理平台。
+	• 針對實際遇到的問題進行研究、分析並提出技術解決方案。
+【職務特色】
+	• 以資料工程、軟體開發及資訊系統建置為主要發展方向。
+	• 部門目前處於架構建立及需求探索階段，具有高度發揮空間。
+	• 不侷限於既有流程，可參與</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96jqm</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>【工程部】消費事業群｜資深資料工程師 - 消費數據 Senior Data Engineer（JIRA854）</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>全曜財經資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>新北市板橋區 文化路一段268號12樓</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Cloud 與 On-premise 之間做出合理架構選擇的資深數據工程師。
+【工作內容】
+1. 建置消費 Raw Data 的資料基礎：從 MongoDB 等 Source System 進行資料擷取、清理、轉換與儲存，建立穩定、可追蹤且可擴展的</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9516t</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>20261011</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>量化交易資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>宏穩資本股份有限公司</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>其他投資理財相關業</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>台北市信義區 松仁路32號14樓之1</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>月薪 1,200,000元以上</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 熟悉 Linux、Git 與基本軟體工程實務，包括程式碼審查、測試、日誌及監控。
+* 理解時間序列資料的處理方式，能妥善處理時間戳、時區、資料排序及跨來源對齊。
+* 重視資料正確性與可追溯性，具備獨立排查問題及跨團隊溝通能力。
+* 對金融市場</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>資料工程師</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>新北市土城區 中山路3之2號</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>負責企業資料治理架構、數據品質與安全合規的系統開發、規則落實與日常維護，以提升數據資產的信任度、安全性與數據驅動的營運效率。</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92zyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>資料工程師 (IDS-DSS)</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.協助Python、Java、.NET 相關應用程式開發與建置。
+2.協助開發與建置資料庫維護(MSSQL、Oracle)
+3.AI創新技術架構研發，整合各類業務應用
+4.有良好的溝通與表達能力，個性主動積極、具團隊合作精神。
+</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/93nrk</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>數據工程師(台北/台中)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>科雅光電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>台北市南港區 經貿二路198號2樓</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1.針對數據中台的系統進行ETL資料擷轉程式的開發及Report的開發。
+2.建置Data Warehouse的數據模型，執行多維度分析。
+3.對AI的工具進行POC模擬測試及建置。</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96fjo</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>【新莊總部】資深數據工程師</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>勤誠興業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>新北市新莊區 中原路558號19F</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>1.	跨系統資料梳理與 Data Mapping：
+－梳理集團內部 ERP (Oracle/EBS)、MES、PLM、SRM、QMS 等結構化與非結構化數據 
+－規劃並統一跨系統資料表對應邏輯 (Schema Mapping)，消滅資料孤島 
+2</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ym8w</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>產品三部 | 資料工程師(高雄)</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>騰雲科技服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 中華四路45號2樓</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>✅ 工作內容｜你會負責的任務
+1.數據建模：負責設計與維護 MDP 平台的資料模型，確保能有效支撐財務、銷售、行為等多維度主題數據。
+2.ETL 流程開發：配合使用 ETL 工具，撰寫高效能的 T-SQL 邏輯進行數據清洗、轉換與載入。
+3.效能</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xvzb</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>20261006</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>品管工程師(高雄地區)</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>睿程營造工程股份有限公司</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>其他營造業</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高雄市鼓山區 </t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>1. 負責各計畫書編製及送審。
+2. 契約材料設備自檢及施工自檢。
+3. 設計圖、標單及施工規範校對，並編撰施工圖。
+4. 每日工程施工內容及進貨材料清單統計彙整。
+5. 製作甲方(業主)估驗計價資料自檢及查驗資料、校核協力廠商請款資料及相關表單</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85srh</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>20260621</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>軟體開發工程師</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>嘉聯益科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>印刷電路板製造業(PCB)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>新北市樹林區 博愛街248號</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1、內部AI 系統之分析、設計與開發工作。
+2、AI 模型與服務的測試、效能調校與持續優化工作。
+3、負責軟體架構規劃與模組設計、制定開發規範並有效管控專案進度，以確保系統可擴展性與穩定性。
+4、推動新平台功能與端到端產品體驗的完整產品開發生命週期。
+</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92w1u</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>全電商營運部-數據工程師</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>全聯福利中心_全聯實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>量販流通相關業</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>台北市中山區 敬業四路33號</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>加入我們！
+數據工程師的核心挑戰與工作內容：
+1. 數據處理與自動化 — 了解與整合異質數據來源（API、DB資料庫、CSV、Parquet 等），建立高可靠度的 ETL／ELT 數據自動化處理流程、部署與監控機制，確保服務穩定性 
+2. CDP</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8mp6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>IT-Data Engineer數據工程師(後端開發)_新北土城</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>鴻佰科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>電腦及其週邊設備製造業</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新北市土城區 </t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>1.ETL的數據接入、清洗與匯入
+2.數據倉庫的建模與標準化
+3.後端API對接
+4.系統自動化代碼持續整合/持續部署
+5.系統效能調校/監控
+6.支援IT專案任務及主管交辦事項。</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pnyc</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>資料工程師(竹科)</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>前進國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">新竹市 </t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>ETL Job Migration</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x2u8</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>資料整合副工程師</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>台灣美日先進光罩股份有限公司</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>半導體製造業</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>新竹市 力行路2號1樓(300)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>月薪 33,000元以上</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>IQC team：
+✓客戶資料下載及文件彙整
+✓進案資訊異常分析及回饋
+✓生產管理系統資料輸入及檢查
+✓客戶資料異動的辨別與解讀
+TP1 team：
+✓光罩資料轉檔
+✓提供光罩檢驗資料
+✓依照需求提供Remote JDV資料
+✓支援異地工廠的光罩</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/2om9y</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>資料工程師-M115</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>精誠軟體服務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>台北市中山區 松江路96號21樓</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>加入專案團隊，協助規劃、建置與優化企業資料處理與分析所需的資料基礎，主要任務包含：
+1. 設計、開發並維運資料整合流程，涵蓋 ETL／ELT 作業、資料清理、格式轉換與流程監控。
+2. 串接多元資料來源，進行資料模型、資料表結構與處理邏輯的設計與</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7mqfz</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>遊戲資料庫工程師</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>吉恩立數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段106號5樓</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>我們找的就是你：善於溝通、邏輯清晰及執行力的工程師 !
+負責一款遊戲，
+從資料庫初期的建置發佈以及遊戲整體環境建置，到後續服務的長久運行管理。
+在這裡你不會感到孤單，會有同仁一起參與合作與營運，當然，熟悉後也有需要獨自運作的時刻。
+【工作任務</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8tymj</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>AI Data Engineer AI 資料工程師</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>摩速科技有限公司</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>台北市大安區 仁愛路三段17號3樓</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>性、可解釋性、結果正確性
+- 調查資料異常與不一致問題，找出根本原因，並建立可持續的預防與監控機制。
+- 與產品、商務與工程團隊合作，對齊資料定義並交付關鍵資料資產。
+- 建立或延伸 AI 產品功能，例如：Agent workflow、推薦邏輯、自</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91odq</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Data Engineer / 資深資料工程師(Python)</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>宇利峯有限公司</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>台中市西屯區 市政路386號</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>職位概要:
+我們正在尋找一位專精於資料整理和Python開發的Python資料工程師，主要負責資料的清洗、標準化和品質控制工作。
+1. 數據清洗和標準化:
+- 處理原始資料，識別和處理異常值。
+- 統一資料格式和編碼標準。
+- 補齊缺失值和修正</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>海沃控股股份有限公司</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>高雄市苓雅區 青年一路193號3樓</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>1.清理與處理各種來源的原始資料（格式混亂、品質不一都是常態），整理成訓練可用的資料集。
+2.協助定義「什麼是好的資料」，建立資料品質標準，並實際把關。
+3.持續了解與追蹤什麼樣的資料能幫助模型訓練出更好的效果，回饋到資料策略。
+4.依訓練需求生</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/967ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>[ Python ] Senior Data Engineer 資料工程師  #Data &amp; AI  #ACT年度敏捷組織</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>炬識科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>台北市中山區 長安東路一段23號3樓</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Athemaster 以 MetaRoots 與 DQSentry 為核心，服務金融與零售企業，打造高擴充性的資料平台與品質監控框架，從 DataOps 到 AI 應用，挑戰真實企業級資料環境。
+▎你想知道的 Athemaster：</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7kabt</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>BI 資料工程師 (IDS-BAS)</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>宏燁資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>台北市中正區 北平東路30號7樓</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>1.參與數據中台整合專案開發與維運。 
+2.協助建置與維護 ETL/ELT 數據管道。 
+3.使用 SQL、Python 進行資料擷取、轉換及清理作業。 
+4.協助雲端數據平台開發與測試。 
+5.參與Data Warehouse 及</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ip4q</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>資料工程師  Data Engineer</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>數解人意科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路三段 195 號 7 樓</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>專科、大學</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>【 資料工程師 ( Data Engineer) 】
+在 QSearch，數據是我們最核心的資產。此角色的核心目標是建構公司大數據生態系的「源頭引擎」。您將負責設計、開發與維運可擴展的高速分散式爬蟲系統，與各平台反爬蟲機制正面對決，並優化高併發</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92847</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Data Engineer 數據工程師(錦州街)</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>山富國際旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>台北市中山區 錦州街46號10樓</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>月薪 48,000元以上</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">與效能調校。
+與後端工程師協作，確保數據收集與儲存的效率與規範。
+探索並導入新興的數據技術與工具，持續提升團隊的數據處理能力。
+</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/73ifb</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>機器人學習應用工程師</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>伊士博國際商業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>半導體製造業</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>新竹市 東區東光路13號</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>月薪 55,000 ~ 80,000元</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>我們正在招募具備 AI Manipulation 專業背景的機器人學習應用工程師加入我們新技術開發團隊
+您將負責協作機器人自動化規劃並實作可處理複雜行為的操控與抓握功能，依位置估測、路徑規劃與機械、軟體及韌體、硬體單位協作，完成系統測試和專案模擬</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8pj1w</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>(C6) 資深數據工程師Senior Data Engineer（內湖）</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>鴻海精密工業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>消費性電子產品製造業</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>【職位說明】
+參與智慧城市 AI 賦能產品開發，負責建置企業級數據平台(Data as a Service, DaaS)，處理各種形式的資料，並進行完善的資料治理、血緣追蹤與監控。最終將整合生成式 AI（Generative AI）功能，提供智慧</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p0av</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>資料工程師 Data Engineer</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>英屬開曼群島商萬里雲互聯股份有限公司台灣分公司</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>台北市信義區 基隆路一段333號33樓</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>【職務說明】
+       我們正在尋找一位具備高度專業技能的資深資料工程師，加入我們快速成長的資料與AI解決方案團隊。此角色將負責設計並交付可擴展的資料平台、建置資料管道，並推動雲端/地端環境下的資料搬遷，以銜接AI分析應用落地。</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8p7ye</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>【國泰集團】資料科學工程師 (數據應用工程師) – (數數發中心, DDT)_I00020717</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>國泰世紀產物保險股份有限公司</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>產物保險業</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>月薪 44,000元以上</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+* 目標成果導向：重視成果並具合作互助精神
+* 積極主動、持續進步：樂於學習與自我成長
+* 熱愛數據、對技術充滿熱忱：積極探索與應用新技術
+【工作內容】
+資料工程的世界千變萬化，以下是你的任務指南：
+1. 數據蒐集與處理，接觸各種資料來源，進行</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8n8v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>資料探勘工程師 / Data Mining Engineer</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>禾多移動多媒體股份有限公司</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>數位內容產業</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>台北市中山區 中山北路三段47號5樓之4</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I285">
+        <f>======================================
+【Job Description】
+• 數據收集與整合： 從各種來源 (如資料庫與API 等) 收集數據，並將其整合到統一的數據倉庫或資料湖中。
+• 數據清理與轉換</f>
+        <v/>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4u9yz</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>【PayEasy】資料工程師_4151</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>PayEasy_康迅數位整合股份有限公司</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路二段9號2樓</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>理效能與架構。
+4.與數據工程師、數據分析師、商業分析師密切協作，理解各方需求並提供對應的資料表與 API。
+5.負責專案型的資料建置，並規劃與設計既有（舊）資料結構的翻新與優化。
+6.建立並維護資料字典、文件與資料治理規範（權限、保存政策、隱私合</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/942ru</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>數位醫療服務 -【資料分析 / 資料工程師】</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>采鋐健康整合集團_采照策略顧問股份有限公司</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>台北市信義區 信義路五段5號M層</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>這不是一份只會「做報表」的工作。 我們正在尋找一位能夠把資料玩出火花的夥伴，讓數據真正變成影響決策的武器！
+你將會：
+1. 透過 Tableau、Looker、PowerBI 等 BI 工具，打造一眼就能看懂的超強報表，讓老闆和團隊秒懂數據價值。</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8te5p</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>資深測試工程師-Sr. Test Engineer-BT</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>博思顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>台北市南港區 市民大道7段8號</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>年薪 1,000,000 ~ 1,600,000元</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>6年以上</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>【職位簡介】
+我們是一間軟體開發公司，致力於打造創新產品與沉浸式數位體驗，服務全球用戶。
+我們正在尋找一位細心且邏輯思維強的【測試工程師】，協助設計並執行手動與自動化測試流程，確保每一項產品在推出前達到穩定、可靠且高品質的標準
+【主要職責】
+．</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8v9e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20261005</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>國外業務工程師</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>久誼股份有限公司</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>加工紙製造業</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>台中市外埔區 長生路806號(工作地點距離台中新光三越-開車25分鐘(走高速公路)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>1.熟悉欲銷售之產品
+2.以顧客熟悉之語言做顧客市場開發並推銷產品
+3.市場訊息的蒐集與分析、客戶銷售方案的策劃與執行
+4.依顧客需求報價及簽約、客戶關係的維護與需求服務的滿足
+5.顧客售後滿意度維持 (如: 顧客抱怨及問題反應處理、維持顧客對公司及業務員信賴度)
+6.意見回饋以供公司改善參考依據
+7.定期與主管做業績、績效檢討，回報進度，每月依據業績績效達標後給予業務獎金。
+8.定期於國內或國外展覽會場開發顧客
+9.完成公司及主管交辦事項
+10.獎金制度完整
+※具標籤、膠帶、複合材料、塗佈、製紙等相關產業經驗者尤佳</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6okra</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>20260728</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>數據工程師｜AI產業｜新創｜Python｜歡迎新鮮人與資深開發者</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>睿思智慧股份有限公司</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>新北市板橋區 中山路2段443巷77號10樓</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>最佳夥伴。未來也將持續擴展Neuro家族，讓AI應用更親民、更普及。
+如果你喜歡學習、願意動手做事，歡迎加入我們，一起努力成長，創造更多可能！
+【主要任務】
+1. 與資料科學家、雲端架構師、資料分析師及專案經理密切合作，提供高品質的雲端數據服務給</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8xq4h</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>研發工程師(全端、資料、後端研發)</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>宇數科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>台北市中山區 長春路176號</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>宇數科技是一家致力於提供全方位資安保護方案的專業技術公司。我們相信員工的培育是企業永續發展的關鍵因素，因此致力於提供完善的技能培訓制度和持續成長。
+★ 資料、後端、全端工程師
+1. 熟悉 Machine Learning 開發經驗。
+2. 能獨</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81zme</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>【數轉院/綠色製成科技中心】資料工程師</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>資策會_財團法人資訊工業策進會</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>南投縣南投市 文獻路2號(中創園區)</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.協助工廠內部大數據應用、分析及監測相關應用，可進行數據分析。
+2.透過軟體開發加速工廠相關作業流程。
+3.研發論文搜尋、閱讀及技術分享。
+4.計畫、教育訓練及技術轉移等技術文件撰寫。
+5.科技趨勢研究、專利提案及撰寫專案計畫規格。
+</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/966a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>資料平台工程師</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>愛普智科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>育樂用品製造業</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>台中市大甲區 中山路二段901號</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>資料分析師、BI 工程師緊密協作，親手打造公司的資料骨幹。
+主要職責
+•	負責雲端資料庫（Microsoft Fabric）的備份、還原、災難復原與存取權限控管
+•	監控資料庫效能與容量成本，進行調校與優化
+•	作為 SAP 資料需求窗口，與總部</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96aci</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>資料工程師(部分工作遠端)-視訊面試</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>碩成有限公司</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台中市西屯區 </t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>月薪 43,000 ~ 68,000元</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備資料工程實務經驗、熟悉 SQL 與 Python 的「資料工程師」加入團隊！
+如果你喜歡處理資料、建立穩定的資料流程，也能與數據分析師溝通需求並將分析需求轉化為實際的資料處理方案，歡迎加入我們，一起打造穩定、可靠且可維護的</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/95mv5</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Data Engineer (Mid Level)  資料工程師（中階）</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>極酷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>其它軟體及網路相關業</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>台北市中正區 忠孝東路2段26號2樓</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✨加入 KICKS CREW，與我們一起成長！CAN'T STOP WON'T STOP✨
+We are a rapidly growing global e-commerce platform specializing in sneakers and apparel. Our engineering team is committed to building cutting-edge technologies that continuously transform how customers discover, shop, and engage with our platform.
+We are looking for a Data Engineer with 3+ years of experience building and optimizing data infrastructure. This role will focus on BigQuery warehouse optimization, event tracking quality, and scalable data pipeline design.
+✨Key Responsibilities
+Data Warehouse Optimization
+• Optimize and refactor BigQuery data models for performance and cost efficiency
+• Improve table structure, partitioning, clustering, and query performance
+• Maintain and enhance ELT pipelines
+• Enforce data quality checks and documentation standards
+Event Tracking Quality
+• Audit and redesign Mixpanel and GA4 tracking architecture
+• Validate GTM, SDK, and server-side event implementation (QA Process)
+• Standardize event naming and tracking schema
+• Identify and close tracking gaps
+Data Pipeline &amp; Integration
+• Build and maintain scalable data pipelines into BigQuery
+• Handle structured and semi-structured data
+• Support cross-domain data integration
+BAU &amp; Collaboration
+• Support BI team on optimization-related data requests
+• Troubleshoot discrepancies across warehouse and tracking tools
+• Document data lineage and ownership
+✨Requirements
+Experience
+• Minimum 3 years of experience as Data Engineer or similar role
+• Strong hands-on experience with cloud warehouse.
+• Experience with event tracking architecture and debugging (QA)
+Technical Skills
+• SQL/Programming Proficiency
+• Workflow Orchestration (e.g Apache/Airflow/Dagster, etc)
+• Experience with ETL or ELT pipeline design
+• Familiar with event-based tracking models
+• Understanding of data modeling and warehouse best practices
+Nice to Have
+• Experience with the modern data stack (e.g., dbt, Airbyte, Datahub)
+• Familiarity with Docker and Kubernetes
+• Experience integrating and managing Mixpanel and GA4 data
+</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90m7j</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>數據工程師 - WS215</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>朋昶數位科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>台北市中山區 民生東路三段51號5樓</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>1.  參與 Data Migration 專案規劃與執行。
+2.  負責既有 SQL 程式分析、修改及優化。
+3.  負責 ETL 流程開發、修改、測試及維護。
+4.  進行來源系統與目標系統之資料整合及轉換設計。
+5.  撰寫 Stored</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92xr1</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>評鑑組專任計畫助理(資料工程師)</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>東吳大學</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>台北市士林區 臨溪路70號</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>月薪 36,300 ~ 41,500元</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.校務資料庫定期更新、維護與管理。
+2. 協助校務研究專案申請、資料分析與成果彙整。
+3. 協助辦理校務研究計畫與專案申請。
+4. 中心相關活動辦理及行政支援。
+5. 其他主管交辦事項。	</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92136</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>CRM數據工程師</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>忠泰建設股份有限公司</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>建築工程業</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>台北市大安區 市民大道三段178號8樓</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>專科</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>1.	集團數據中台建設與管理：
+-	設計並執行跨系統資料管道（ETL），將多公司數據清洗、標準化後匯入集團 CRM，優化整體資訊流。
+-	制定集團數據標準規範，負責資料庫（SQL/NoSQL）效能優化與生命週期管理。
+-	主導資料去識別化與資安合</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/91241</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>資料工程師 (資料治理/ETL)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>聯合通商電子商務股份有限公司</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段69號8樓</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>1. 使用 ETL工具開發或是資料庫/資料表系統相關之程式設計及開發
+2. 依規格設計開發包含 SQL Script 以及 Store Procedure 等對資料進行處理的程式，並進行UT測試，撰寫驗證報告
+3. 資料管理與處理相關專案之需求訪</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/81zdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>資料/數據工程師 Data engineer</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>新加坡商西拉雅科技有限公司</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>台北市信義區 松仁路89號4樓之4</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>【關於本職缺｜About the Role】
+Data Engineer 是公司資料基礎建設的核心角色，負責建置、維護與優化資料管線、資料倉儲與數據工程架構，確保來自 GTM、RevOps 與各商務系統的資料能被穩定整合、清洗、轉換並提供給分析與</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/962as</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>資訊處_數據工程師</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>美而快實業股份有限公司</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品零售業</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路203巷29號</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>專科以上</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Analytics 4（GA4）
+Matomo
+數據處理與資料工程
+Databricks、Azure Blob Storage
+parquet 資料格式處理
+Dagster、Talend
+資料庫與後端處理
+Microsoft SQL</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6sqki</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>BI 數據工程師  (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>神來也麻將_慧邦科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>台北市中正區 羅斯福路二段100號10樓</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>1. 建置與維運遊戲數據 ETL / ELT 排程。
+2. 與分析、PM、營運合作，提供即時數據查找並建置固定排程或後台功能。
+3. 進行資料品質檢查、異常偵測與基礎探索分析。
+4. 開發與維護數據後台、API 與資料平台相關功能。
+【專業條</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/6u7bu</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>生成式AI應用工程師（LLM／RAG／AI Agent／資料平台）</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>國立成功大學_醫學院藥理學研究所</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>台南市東區 大學路1號</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>成大共研中心研究計畫誠徵生成式AI應用工程師（LLM／RAG／AI Agent／資料平台）
+1. 生成式AI應用開發與整合：
+串接 OpenAI API 或開源大型語言模型，運用 Dify 等平台設計及開發 RAG（檢索增強生成）流程，將數據中</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/95z85</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>雲端應用數據工程師｜打造零售產業的智慧雲端數據平台</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>統一資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>台北市內湖區 石潭路155號8F~10F</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>你對雲端架構、大數據平台充滿熱情嗎？
+加入我們，一起建構零售集團的雲端數據平台，讓資料真正成為商業決策的即時助力！
+在這份工作中，你將運用雲端原生服務、程式開發能力與產業知識，與 infra 團隊緊密合作，打造穩定、高效、可擴展的數據環境。這份工</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/85s8z</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>AI工程師 (台南)</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>汎海科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>其他電子零組件相關業</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>台南市新市區 中信半導體學院</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Python 後端工程師 / 技術合夥人（SaaS 平台）
+我們不是找員工，而是找一起打造產業平台的夥伴。
+SaaS 後端架構設計
+設計 Multi-tenant 架構
+API 設計與版本控管
+JWT 認證與權限系統
+製程邏輯設計
+可擴充架構規劃</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8molw</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>20261009</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Data Engineer 資料工程師_ENG Center</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Gogoro Taiwan Limited_睿能創意股份有限公司</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>機車及其零件製造業</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>台北市松山區 長安東路二段225號 (或桃園市龜山區頂湖路33號)</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>職務影響力
+本職位以資料工程與分析平台建設為核心，負責打造穩定、可擴展且可維運的工程數據基礎設施，作為工程與研發團隊進行數據決策的關鍵支撐。透過提升資料管道品質、系統自動化與整體擴展性，使資料分析工程師與工程團隊能在一致且可信的數據基礎上，規模化</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8wzpl</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>20261001</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>數位研發資訊工程師</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>宏于電機股份有限公司</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>自動控制相關業</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>新北市樹林區 武林街2-3號</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主管安排的訓練課程，提升技術能力和工作效率。
+5.歡迎個性積極外向，正面思考的工程師。
+6.有網路或機房管理者尤佳。
+※此工作職務可培訓，須有系統或專案管理工作經驗，學習能力強。
+</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8jfw6</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>AI 數據工程師(Data Engineer / ML Engineer)</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>博訊生物科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>台北市內湖區 內湖路一段250號6樓（晶鑽科技大樓）</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>月薪 50,000元以上</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>【工作職責】
+• 負責梳理與分析資料庫中的數據，找出隱藏的特徵與資料欄位間的關聯性。
+• 運用 SQL 與 Python 進行資料撈取、清理與特徵工程，建立穩定且高效的資料流程序。
+• 開發、訓練並優化具備「高可解釋性」的 AI 預測模型，將分析</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/92ufq</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>泰坦分子生醫股份有限公司</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>生化科技研發業</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>新竹縣竹北市 生醫園區</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>月薪 60,000元以上</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>3年以上</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>我們正在開發新一代快速分子診斷設備，需要一位對「軟體＋UI＋資料分析＋硬體整合」有興趣的工程師，參與從儀器控制、使用者介面到檢測資料分析的完整產品開發。
+1. 負責分子診斷儀器之軟體與使用者介面（UI）開發。
+2. 設計及開發儀器操作流程、檢測</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/94mp9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>20260805</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>網路管理工程師~擴大召募~</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>智偉織造股份有限公司</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>紡織成衣業</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>桃園市中壢區 工業區東園路50號</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>月薪 43,000 ~ 53,000元</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>【工作內容】
+公司機房、網路設備、伺服器之管理
+【職務說明】
+1. MS SQL資料庫管理。
+2. 機房及網路設備管理。
+3. HyperV 虛擬化環境管理架設。
+4. 資訊安全管理及稽核。
+5. 資訊設備故障排除及使用者電腦問題解決。</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/3x4nc</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>職安衛工程師_旭家廠</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>索爾思光電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>光電產業</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>新竹市 水利路81號8樓之8</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>*各項職安衛業務推動、計畫與執行管理
+*職業安全衛生管理系統維護及運作。
+*工作環境危害之辨識、評估及控制
+*採購、變更及承攬管理
+*作業環境監測及化學品管理
+*消防檢查申報、緊急應變規劃及演練
+*職安衛安全衛生相關教育訓練規劃及運作
+*主管交辦事項</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8w5cy</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>IT資料工程師(Data Engineer)</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GARMIN_台灣國際航電股份有限公司</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>電信相關業</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>新北市汐止區 新台五路一段97號37樓</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">【Job Description】
+We are looking for a skilled and motivated IT Data Engineer to join our team in Taiwan. In this role, you will design, build, and maintain scalable data solutions that support reliable data processing, analytics, and business decision-making.
+You will work with modern data technologies such as Spark, Iceberg, Dremio, Kafka, Qlik, and Airflow to build scalable, reliable, and business-oriented data platforms.
+This role is ideal for someone who enjoys solving complex data problems, working across systems and teams, and turning data into practical business value.
+【Responsibilities】
+•	Design, build, and optimize scalable batch and real-time data pipelines. 
+•	Develop and maintain data models, data warehouses, and lakehouse solutions. 
+•	Build reliable data orchestration and workflow automation processes. 
+•	Work with business and IT teams to deliver data solutions, dashboards, and analytics use cases. 
+•	Support BI, reporting, and self-service analytics through tools such as Qlik. 
+•	Improve data platform reliability through monitoring, troubleshooting, scripting, and automation.
+【Skills】
+1. Essential
+•	Hands-on experience with Spark for large-scale data processing.
+•	Experience with Iceberg, Dremio, or similar lakehouse / modern data platform technologies.
+•	Experience with Kafka or other streaming data technologies.
+•	Strong SQL skills and experience with databases such as Oracle, MSSQL, or PostgreSQL.
+•	Proficiency in Python or Scala for data processing and automation.
+•	Experience with workflow orchestration tools such as Airflow or similar scheduling tools.
+•	Understanding of data modeling, data warehousing, and lakehouse architecture.
+•	Experience with BI or analytics tools such as Qlik, Tableau, or Power BI.
+•	Familiarity with Docker, Kubernetes, Linux, and shell scripting.
+2. Desirable / Nice to Have
+•	Experience with Hadoop or legacy big data platforms.
+•	Experience with S3-compatible object storage or large-scale data lake environments.
+•	Ability to develop and deploy REST APIs or web services.
+•	Familiarity with AI/ML pipelines and related data preparation processes.
+•	Experience or strong interest in GraphDB / Knowledge Graph concepts, including entity relationship modeling, relationship discovery, and graph-based analysis.
+3. Preferred Skills
+•	Strong analytical and problem-solving skills.
+•	Good communication and cross-functional collaboration abilities.
+•	Detail-oriented, proactive, and comfortable working in a fast-paced environment.
+•	Willingness to learn new technologies and continuously improve data solutions.
+</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7z55c</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>資料庫工程師-DBA</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>錦鉅城股份有限公司</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>網際網路相關業</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>台中市南屯區 大墩十街300號10樓</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>大學</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>1. 熟 MongoDB、SQL Server、MySQL、 建置、管理、維護。 
+2. T-SQL 及 Stored Procedure 效能調校。 
+3. 資料庫日常監控、異常排除及系統性能優化。 
+4. 具 DB HA 架構建置和維護經驗。</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8x1vk</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>AI資料工程師</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>松凌科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>台北市中正區 衡陽路51號7樓之11</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>月薪 45,000元以上</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>我們協助企業把散落各處的資料整合、轉換成可信賴的決策依據。你會參與從資料管線設計到報表產出的完整流程，並實際將 AI 工具導入日常開發，提升團隊效率。
+主要工作內容
+1. 開發資料轉換（ETL）程式，並驗證資料正確性
+2. 依業務需求開發報表，</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/79ccc</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>AI+BI 大數據工程師</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>天應資訊顧問有限公司</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>台北市大安區 和平東路二段53巷2號6樓</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>月薪 40,000元以上</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 開發資料介接數據分析引擎(熟 Python 語法及資料庫SQL語法。
+2. 資料視覺化設計及開發。
+3. ETL 設計及開發。
+4. 資料管理及分析
+5. 系統測試及維護
+6. 文件製作
+</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/38q85</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>資料分析工程師</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>嘉德高分子應用材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>橡膠製品製造業</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>新竹縣湖口鄉 鳳工路45號2樓</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 70,000元</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>專科、大學、碩士</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>要能實現目標，語言、框架、資料庫與硬體規格皆由團隊討論決定。
+無歷史包袱： 系統從 0 開荒，不需維護古老的舊程式碼。
+資料工程師在現今數位化時代扮演著重要的角色，負責設計、開發、建置企業級大數據平臺、資料倉儲及相關服務，為企業提供更好的資料</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/946sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>AI轉譯團隊-生醫資料工程師/資料科學家Biomedical Knowledge &amp; Data Engineer【製藥研究所】</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>中化控股_中國化學製藥股份有限公司</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>藥品製造業</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>新竹縣新豐鄉 上坑村坑子口182-1號</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>職務價值：落實全地端部署，打造可溯源、可驗證的生醫知識系統，降低AI模型幻覺與資料外洩風險。
+工作職責：
+1.蒐集、清理及整合PubChem、DrugBank等公開生醫資料庫，建立標準化資料處理流程與生醫知識圖譜。
+2.建置地端多代理系統（</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/96043</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>軟體工程師</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>先鋒機械股份有限公司</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>金屬加工用機械製造修配業</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>新北市土城區 民族路9號</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>月薪 45,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>容：
+● 資料處理：使用 Python、OpenCV、NumPy 等進行資料特徵分析。
+● 感測器系統整合：感測器整合與系統串接。
+● 系統開發與優化：撰寫與優化系統性能、API 設計
+基本條件：
+● 具備 Linux 作業系統環境經驗。
+● 了</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8ocyj</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>【Actuarial Engineer】精算工程師</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>艾米茲科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>台北市中正區 南海路1號13樓</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>月薪 60,000 ~ 85,000元</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>高中職、專科、大學、碩士、博士</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>模組（如 Python、R、SQL）
+✹ 與資料工程師合作設計精算資訊自動化流程（ETL、報表產出、維運）
+✹ 開發與維護精算假設、定價模型與損益分析框架
+✹ 支援保險公司或金融機構的系統導入與驗證專案
+✹ 撰寫技術文件與精算模型說明書
+【必要條</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8usfi</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>【台中】資料工程師</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>敦謙國際智能股份有限公司</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>台中市西區 國泰金融大樓(台中市西區英才路 530 號) 24 樓</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>月薪 42,000 ~ 90,000元</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>職務工作內容：
+營運策略系統 (RMS)
+透過資料分析、資料探勘和數據處理技術，為旅宿提供精準的營運決策依據。
+建模預測，根據歷史銷售資料，建立銷售量、住宿率等預測模型，為旅宿決策的制定提供參考。
+協助開發專為旅宿設計的智能客服機器人。
+職務需</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/75oc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>20261007</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>資安數據工程師 (Junior) Security Data Engineer</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>動力安全資訊股份有限公司</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Looking For】
+我們相信態度與潛力比經驗更重要，希望你具備以下特質：
+● 資訊工程、資訊管理、資訊安全或相關科系背景（學士以上），具備扎實的計算機基礎 —— 作業系統、網路協定與資料庫概念。
+● 熟悉 Linux 基本操作與 Shell</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4jnp8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>20261002</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>大數據部門數據工程師</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>典通股份有限公司</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>工商顧問服務業</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>台北市中正區 愛國西路9號7樓</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>1.數據清洗、加工、分類等開發工作，運用數據演算法及工具對數據進行挖掘工作。
+2.數據模型的規劃並進行數據分析，支持應用端資料分析與預測。透過機器學習、深度學習、資料探勘、大數據分析等技術建立預測模型，或進行文字探勘、語意分析等任務。
+3.參與客</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/7763m</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>數據分析工程師</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>馗鼎奈米科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>其他半導體相關業</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>台南市永康區 永科環路255號</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 65,000元</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>碩士</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>1. 協助單位分析數據、建立模型、數據視覺化，並協同轉化成可執行方案，並追蹤方案成效
+2. 專案管理：協助平行展開設備智慧化專案開發
+3. 具Python程式撰寫能力，熟悉資料分析技術(統計學、機器學習、深度學習、強化學習、等)者佳
+4. 具備設</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8d2ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>20260831</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>【資訊板塊】金融數據工程師(企業資料倉儲整合｜核心系統現代化｜數據架構轉型)_I00024956</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>國泰世華商業銀行股份有限公司</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>銀行業</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市內湖區 </t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>打造金融數據新未來，從你開始！
+你相信數據不只是冰冷的數字，而是能驅動決策、創造價值的力量嗎？
+在這裡，你不只是寫程式，而是參與一場金融數據革命！
+加入我們，打造穩定、高效、可擴展的資料平台，讓每一筆數據都能說故事，讓你的技術真正改變企業未來。</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8whwf</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>20261012</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>資訊處_數據工程師</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>美而快國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>鞋類／布類／服飾品零售業</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>台北市南港區 重陽路203巷29號</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>5年以上</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Analytics 4（GA4）
+Matomo
+數據處理與資料工程
+Databricks、Azure Blob Storage
+parquet 資料格式處理
+Dagster、Talend
+資料庫與後端處理
+Microsoft SQL</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90ruo</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>數據工程師(台北)</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>前進國際股份有限公司</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">台北市大安區 </t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>- 具2年以上ETL/資料管線Airflow、BigQuery、DataForm實作經驗，並可於面談時展示相關專案。
+- 具使用Python和數據庫管理(SQL)的經驗。
+- 了解GCP於雲端平台開發經驗或具學習經驗。</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/90xqh</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>20261013</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>數據工程師</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>可樂旅遊旅行社股份有限公司</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>旅遊服務業</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>台北市中山區 南京東路二段90號12樓</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>資料運用並創造商業價值，並積極探索 AI 技術，提升整體營運效率與決策品質。
+【工作內容】
+1. 設計、開發與維護數據流程，打造穩定且高效的數據基礎架構
+2. 使用 Python 進行數據清理、轉換與處理
+3. 將數據處理流程自動化，並協助部署至雲</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/853np</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>研發工程師 【智慧製造研究中心】</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>國立成功大學_研究總中心</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>大專校院教育事業</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>台南市東區 大學路一號自強校區儀器設備大樓6樓95610室</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>大學、碩士</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>1. 工業工程相關科系
+2. 具備作業研究與最佳化理論經驗
+3. 具備機器學習與深度學習理論基礎
+4. 具備python程式語寫撰寫能力
+5. 研發替代役可</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/4zgrz</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>20260930</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>FDE （Ai前線部署工程師）</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>幻翔商用設計有限公司</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>專門設計相關業</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>台南市永康區 中正南路416號</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>月薪 35,000 ~ 80,000元</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>1年以上</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>就業主品牌！
+我們的工程團隊是你的後盾，你負責科技輸出！
+•	拒絕傳統科技業的枯燥：你不必在科技廠當一顆螺絲丁。在這裡，你的 AI 部署會直接幫助設計師、工程師和品牌客戶，讓科技真正落地在有趣的商業場景中。
+•	最友善的跨界合作環境：我們有專業的</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/9351g</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Scientific Computing Engineer 科學運算工程師</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>安瑟樂威股份有限公司</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>電腦系統整合服務業</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>台北市中正區 新生南路一段50號四樓之5</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>待遇面議</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>不拘</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>碩士、博士</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 資料分析能力（Data Analysis）：
+   a. 統計推論、視覺化溝通、資料品質監控、實驗設計與因果推論
+   b. 期待深度：AI 跑出一組統計結果，你能判斷假設檢定的前提是否成立、視覺化有沒有誤導、因果方向有沒有搞反。
+工程類（至少</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/95vhs</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>20261014</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>資料庫工程師(部分遠端工作)-視訊面試</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>碩成有限公司</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>電腦軟體服務業</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>台中市西屯區 臺灣大道三段540號14樓之1</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>月薪 40,000 ~ 69,000元</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2年以上</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>大學以上</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>我們正在尋找一位具備資料庫維運經驗的「DBA 資料庫管理工程師」加入團隊！
+如果你熟悉資料庫管理、效能監控與問題排查，也對資料庫架構及系統穩定性有興趣，歡迎加入我們！
+在這個職位中，你將參與資料庫建置、備份還原、效能監控及故障排除等工作，一起</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://www.104.com.tw/job/8nqsc</t>
         </is>
       </c>
     </row>
